--- a/FullBrushTireForces.xlsx
+++ b/FullBrushTireForces.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\JamesEngine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093B0D6D-5B68-4110-8F2D-08FF114849ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6157E67E-082D-4404-9C85-F9E86ED10890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{69B88305-7471-4B29-B417-11FB95EBCF15}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{44D3E767-952D-48F3-B15C-D19205B365C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -174,10 +174,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$150</c:f>
+              <c:f>Sheet1!$A$2:$A$151</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="149"/>
+                <c:ptCount val="150"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -624,16 +624,19 @@
                 </c:pt>
                 <c:pt idx="148">
                   <c:v>0.25829999999999997</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.2601</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$150</c:f>
+              <c:f>Sheet1!$B$2:$B$151</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="149"/>
+                <c:ptCount val="150"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -659,427 +662,430 @@
                   <c:v>4031.9115999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4598.5825000000004</c:v>
+                  <c:v>4595.9242999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5065.4717000000001</c:v>
+                  <c:v>5036.4492</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5438.9893000000002</c:v>
+                  <c:v>5369.9204</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5744.6005999999998</c:v>
+                  <c:v>5631.2938999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5999.2826999999997</c:v>
+                  <c:v>5841.8608000000004</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6214.7885999999999</c:v>
+                  <c:v>6015.2943999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6399.5117</c:v>
+                  <c:v>6160.7568000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6559.6103999999996</c:v>
+                  <c:v>6284.6201000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6699.7012000000004</c:v>
+                  <c:v>6391.4462999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6823.3140000000003</c:v>
+                  <c:v>6484.5883999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6933.1967999999997</c:v>
+                  <c:v>6566.5698000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7031.5155999999997</c:v>
+                  <c:v>6639.3212999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7120.0063</c:v>
+                  <c:v>6704.3505999999998</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7200.0731999999998</c:v>
+                  <c:v>6762.8505999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7272.8633</c:v>
+                  <c:v>6815.7754000000004</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7339.3275999999996</c:v>
+                  <c:v>6863.9032999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7400.2559000000001</c:v>
+                  <c:v>6907.8716000000004</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7456.3119999999999</c:v>
+                  <c:v>6948.2051000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7508.0591000000004</c:v>
+                  <c:v>6985.3491000000004</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7555.9760999999999</c:v>
+                  <c:v>7019.6719000000003</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7600.4722000000002</c:v>
+                  <c:v>7051.4902000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7641.9027999999998</c:v>
+                  <c:v>7081.0742</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7680.5727999999999</c:v>
+                  <c:v>7108.6543000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7716.75</c:v>
+                  <c:v>7134.4326000000001</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>7750.6688999999997</c:v>
+                  <c:v>7158.5811000000003</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>7782.5342000000001</c:v>
+                  <c:v>7181.2538999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7812.5272999999997</c:v>
+                  <c:v>7202.5839999999998</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>7840.8086000000003</c:v>
+                  <c:v>7222.6899000000003</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>7867.5195000000003</c:v>
+                  <c:v>7241.6747999999998</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>7892.7885999999999</c:v>
+                  <c:v>7259.6318000000001</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>7916.7304999999997</c:v>
+                  <c:v>7276.6436000000003</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>7939.4458000000004</c:v>
+                  <c:v>7292.7842000000001</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7961.0268999999998</c:v>
+                  <c:v>7308.1196</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7981.5576000000001</c:v>
+                  <c:v>7322.7109</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>8001.1117999999997</c:v>
+                  <c:v>7336.6089000000002</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>8019.7578000000003</c:v>
+                  <c:v>7349.8647000000001</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>8037.5581000000002</c:v>
+                  <c:v>7362.5234</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>8054.5684000000001</c:v>
+                  <c:v>7374.6220999999996</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>8070.8413</c:v>
+                  <c:v>7386.1997000000001</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>8086.4228999999996</c:v>
+                  <c:v>7397.29</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>8101.3563999999997</c:v>
+                  <c:v>7407.9228999999996</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>8115.6831000000002</c:v>
+                  <c:v>7418.1255000000001</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>8129.4359999999997</c:v>
+                  <c:v>7427.9242999999997</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>8142.6522999999997</c:v>
+                  <c:v>7437.3446999999996</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>8155.3608000000004</c:v>
+                  <c:v>7446.4071999999996</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>8167.5913</c:v>
+                  <c:v>7455.1318000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>8179.3711000000003</c:v>
+                  <c:v>7463.5385999999999</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>8190.7231000000002</c:v>
+                  <c:v>7471.6436000000003</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>8201.6708999999992</c:v>
+                  <c:v>7479.4629000000004</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>8212.2343999999994</c:v>
+                  <c:v>7487.0117</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>8222.4375</c:v>
+                  <c:v>7494.3062</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>8232.2939000000006</c:v>
+                  <c:v>7501.3563999999997</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>8241.8232000000007</c:v>
+                  <c:v>7508.1747999999998</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>8251.0419999999995</c:v>
+                  <c:v>7514.7754000000004</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>8259.9639000000006</c:v>
+                  <c:v>7521.165</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>8268.6034999999993</c:v>
+                  <c:v>7527.3554999999997</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>8276.9745999999996</c:v>
+                  <c:v>7533.3568999999998</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>8285.0879000000004</c:v>
+                  <c:v>7539.1768000000002</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>8292.9580000000005</c:v>
+                  <c:v>7544.8236999999999</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>8300.5946999999996</c:v>
+                  <c:v>7550.3051999999998</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>8308.0059000000001</c:v>
+                  <c:v>7555.6288999999997</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>8315.2041000000008</c:v>
+                  <c:v>7560.8008</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>8322.1972999999998</c:v>
+                  <c:v>7565.8280999999997</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>8328.9951000000001</c:v>
+                  <c:v>7570.7168000000001</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>8335.6054999999997</c:v>
+                  <c:v>7575.4731000000002</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>8342.0342000000001</c:v>
+                  <c:v>7580.1005999999998</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>8348.2909999999993</c:v>
+                  <c:v>7584.6068999999998</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>8354.3817999999992</c:v>
+                  <c:v>7588.9951000000001</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>8360.3125</c:v>
+                  <c:v>7593.27</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>8366.0918000000001</c:v>
+                  <c:v>7597.4375</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>8371.7217000000001</c:v>
+                  <c:v>7601.4994999999999</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>8377.2109</c:v>
+                  <c:v>7605.4614000000001</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>8382.5653999999995</c:v>
+                  <c:v>7609.3266999999996</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>8387.7852000000003</c:v>
+                  <c:v>7613.0977000000003</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>8392.8809000000001</c:v>
+                  <c:v>7616.7803000000004</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>8397.8534999999993</c:v>
+                  <c:v>7620.3760000000002</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>8402.7090000000007</c:v>
+                  <c:v>7623.8872000000001</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>8407.4521000000004</c:v>
+                  <c:v>7627.3188</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>8412.0840000000007</c:v>
+                  <c:v>7630.6724000000004</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>8416.6113000000005</c:v>
+                  <c:v>7633.9507000000003</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>8421.0352000000003</c:v>
+                  <c:v>7637.1562000000004</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>8425.3623000000007</c:v>
+                  <c:v>7640.2910000000002</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>8429.5928000000004</c:v>
+                  <c:v>7643.3584000000001</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>8433.7304999999997</c:v>
+                  <c:v>7646.3599000000004</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>8437.7811999999994</c:v>
+                  <c:v>7649.2983000000004</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>8441.7440999999999</c:v>
+                  <c:v>7652.1747999999998</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>8445.6239999999998</c:v>
+                  <c:v>7654.9921999999997</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>8449.4208999999992</c:v>
+                  <c:v>7657.7510000000002</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>8453.1416000000008</c:v>
+                  <c:v>7660.4540999999999</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>8456.7860999999994</c:v>
+                  <c:v>7663.1045000000004</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>8460.3554999999997</c:v>
+                  <c:v>7665.7002000000002</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>8463.8554999999997</c:v>
+                  <c:v>7668.2456000000002</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>8467.2852000000003</c:v>
+                  <c:v>7670.7416999999996</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>8470.6465000000007</c:v>
+                  <c:v>7673.1895000000004</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>8473.9434000000001</c:v>
+                  <c:v>7675.5902999999998</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>8477.1777000000002</c:v>
+                  <c:v>7677.9462999999996</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>8480.3505999999998</c:v>
+                  <c:v>7680.2587999999996</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>8483.4629000000004</c:v>
+                  <c:v>7682.5282999999999</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>8486.5175999999992</c:v>
+                  <c:v>7684.7559000000001</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>8489.5146000000004</c:v>
+                  <c:v>7686.9429</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>8492.4590000000007</c:v>
+                  <c:v>7689.0907999999999</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>8495.3477000000003</c:v>
+                  <c:v>7691.2007000000003</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>8498.1864999999998</c:v>
+                  <c:v>7693.2734</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>8500.9735999999994</c:v>
+                  <c:v>7695.3091000000004</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>8503.7119000000002</c:v>
+                  <c:v>7697.3100999999997</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>8506.4022999999997</c:v>
+                  <c:v>7699.2768999999998</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>8509.0458999999992</c:v>
+                  <c:v>7701.2103999999999</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>8511.6435999999994</c:v>
+                  <c:v>7703.1103999999996</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>8514.1991999999991</c:v>
+                  <c:v>7704.9804999999997</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>8516.7090000000007</c:v>
+                  <c:v>7706.8173999999999</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>8519.1787000000004</c:v>
+                  <c:v>7708.6255000000001</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>8521.6074000000008</c:v>
+                  <c:v>7710.4043000000001</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>8523.9961000000003</c:v>
+                  <c:v>7712.1538</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>8526.3446999999996</c:v>
+                  <c:v>7713.875</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>8528.6553000000004</c:v>
+                  <c:v>7715.5698000000002</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>8530.9307000000008</c:v>
+                  <c:v>7717.2372999999998</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>8533.1679999999997</c:v>
+                  <c:v>7718.8788999999997</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>8535.3721000000005</c:v>
+                  <c:v>7720.4951000000001</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>8537.5400000000009</c:v>
+                  <c:v>7722.0864000000001</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>8539.6748000000007</c:v>
+                  <c:v>7723.6538</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>8541.7782999999999</c:v>
+                  <c:v>7725.1986999999999</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>8543.8477000000003</c:v>
+                  <c:v>7726.7191999999995</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>8545.8866999999991</c:v>
+                  <c:v>7728.2168000000001</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>8547.8945000000003</c:v>
+                  <c:v>7729.6934000000001</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>8549.8729999999996</c:v>
+                  <c:v>7731.1475</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>8551.8212999999996</c:v>
+                  <c:v>7732.5806000000002</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>8553.7432000000008</c:v>
+                  <c:v>7733.9937</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>8555.6357000000007</c:v>
+                  <c:v>7735.3856999999998</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>8557.5020000000004</c:v>
+                  <c:v>7736.7587999999996</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>8559.3397999999997</c:v>
+                  <c:v>7738.1127999999999</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>8561.1522999999997</c:v>
+                  <c:v>7739.4462999999996</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>8562.9385000000002</c:v>
+                  <c:v>7740.7622000000001</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>8564.7001999999993</c:v>
+                  <c:v>7742.0600999999997</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>8566.4385000000002</c:v>
+                  <c:v>7743.3402999999998</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>8568.1514000000006</c:v>
+                  <c:v>7744.6035000000002</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>8569.8418000000001</c:v>
+                  <c:v>7745.8495999999996</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>8571.5077999999994</c:v>
+                  <c:v>7747.0785999999998</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>8573.1522999999997</c:v>
+                  <c:v>7748.2924999999996</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>8574.7754000000004</c:v>
+                  <c:v>7749.4897000000001</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>8576.3760000000002</c:v>
+                  <c:v>7750.6698999999999</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>8577.9550999999992</c:v>
+                  <c:v>7751.8364000000001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>7752.9872999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1087,7 +1093,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-034F-4600-962E-78FEE393F244}"/>
+              <c16:uniqueId val="{00000000-6602-4E65-AC3C-B6716E8F3EA3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1099,11 +1105,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2062074447"/>
-        <c:axId val="2062074927"/>
+        <c:axId val="528344528"/>
+        <c:axId val="848240352"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2062074447"/>
+        <c:axId val="528344528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1160,12 +1166,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2062074927"/>
+        <c:crossAx val="848240352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2062074927"/>
+        <c:axId val="848240352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1222,7 +1228,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2062074447"/>
+        <c:crossAx val="528344528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1832,22 +1838,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>19049</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>80961</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>390526</xdr:colOff>
+      <xdr:colOff>447675</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF9C45D1-DD7D-4681-B524-8903CF337F7A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922AB550-0294-99A9-57D8-D3CE9B216D78}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2184,7 +2190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A845A105-BA08-4BE0-A719-88FE68EA7504}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BC353F-650F-4BFE-B177-9E76C1BEF752}">
   <dimension ref="A1:B151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2268,7 +2274,7 @@
         <v>1.4E-2</v>
       </c>
       <c r="B10">
-        <v>4598.5825000000004</v>
+        <v>4595.9242999999997</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,7 +2282,7 @@
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="B11">
-        <v>5065.4717000000001</v>
+        <v>5036.4492</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2284,7 +2290,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="B12">
-        <v>5438.9893000000002</v>
+        <v>5369.9204</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2292,7 +2298,7 @@
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="B13">
-        <v>5744.6005999999998</v>
+        <v>5631.2938999999997</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2300,7 +2306,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="B14">
-        <v>5999.2826999999997</v>
+        <v>5841.8608000000004</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2308,7 +2314,7 @@
         <v>2.2700000000000001E-2</v>
       </c>
       <c r="B15">
-        <v>6214.7885999999999</v>
+        <v>6015.2943999999998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2316,7 +2322,7 @@
         <v>2.4400000000000002E-2</v>
       </c>
       <c r="B16">
-        <v>6399.5117</v>
+        <v>6160.7568000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2324,7 +2330,7 @@
         <v>2.6200000000000001E-2</v>
       </c>
       <c r="B17">
-        <v>6559.6103999999996</v>
+        <v>6284.6201000000001</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2332,7 +2338,7 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="B18">
-        <v>6699.7012000000004</v>
+        <v>6391.4462999999996</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2340,7 +2346,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
       <c r="B19">
-        <v>6823.3140000000003</v>
+        <v>6484.5883999999996</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2348,7 +2354,7 @@
         <v>3.1399999999999997E-2</v>
       </c>
       <c r="B20">
-        <v>6933.1967999999997</v>
+        <v>6566.5698000000002</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2356,7 +2362,7 @@
         <v>3.32E-2</v>
       </c>
       <c r="B21">
-        <v>7031.5155999999997</v>
+        <v>6639.3212999999996</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2364,7 +2370,7 @@
         <v>3.49E-2</v>
       </c>
       <c r="B22">
-        <v>7120.0063</v>
+        <v>6704.3505999999998</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2372,7 +2378,7 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="B23">
-        <v>7200.0731999999998</v>
+        <v>6762.8505999999998</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2380,7 +2386,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="B24">
-        <v>7272.8633</v>
+        <v>6815.7754000000004</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2388,7 +2394,7 @@
         <v>4.0099999999999997E-2</v>
       </c>
       <c r="B25">
-        <v>7339.3275999999996</v>
+        <v>6863.9032999999999</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2396,7 +2402,7 @@
         <v>4.19E-2</v>
       </c>
       <c r="B26">
-        <v>7400.2559000000001</v>
+        <v>6907.8716000000004</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2404,7 +2410,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="B27">
-        <v>7456.3119999999999</v>
+        <v>6948.2051000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2412,7 +2418,7 @@
         <v>4.5400000000000003E-2</v>
       </c>
       <c r="B28">
-        <v>7508.0591000000004</v>
+        <v>6985.3491000000004</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2420,7 +2426,7 @@
         <v>4.7100000000000003E-2</v>
       </c>
       <c r="B29">
-        <v>7555.9760999999999</v>
+        <v>7019.6719000000003</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2428,7 +2434,7 @@
         <v>4.8899999999999999E-2</v>
       </c>
       <c r="B30">
-        <v>7600.4722000000002</v>
+        <v>7051.4902000000002</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2436,7 +2442,7 @@
         <v>5.0599999999999999E-2</v>
       </c>
       <c r="B31">
-        <v>7641.9027999999998</v>
+        <v>7081.0742</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2444,7 +2450,7 @@
         <v>5.2400000000000002E-2</v>
       </c>
       <c r="B32">
-        <v>7680.5727999999999</v>
+        <v>7108.6543000000001</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2452,7 +2458,7 @@
         <v>5.4100000000000002E-2</v>
       </c>
       <c r="B33">
-        <v>7716.75</v>
+        <v>7134.4326000000001</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2460,7 +2466,7 @@
         <v>5.5899999999999998E-2</v>
       </c>
       <c r="B34">
-        <v>7750.6688999999997</v>
+        <v>7158.5811000000003</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2468,7 +2474,7 @@
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="B35">
-        <v>7782.5342000000001</v>
+        <v>7181.2538999999997</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2476,7 +2482,7 @@
         <v>5.9299999999999999E-2</v>
       </c>
       <c r="B36">
-        <v>7812.5272999999997</v>
+        <v>7202.5839999999998</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2484,7 +2490,7 @@
         <v>6.1100000000000002E-2</v>
       </c>
       <c r="B37">
-        <v>7840.8086000000003</v>
+        <v>7222.6899000000003</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2492,7 +2498,7 @@
         <v>6.2799999999999995E-2</v>
       </c>
       <c r="B38">
-        <v>7867.5195000000003</v>
+        <v>7241.6747999999998</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2500,7 +2506,7 @@
         <v>6.4600000000000005E-2</v>
       </c>
       <c r="B39">
-        <v>7892.7885999999999</v>
+        <v>7259.6318000000001</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2508,7 +2514,7 @@
         <v>6.6299999999999998E-2</v>
       </c>
       <c r="B40">
-        <v>7916.7304999999997</v>
+        <v>7276.6436000000003</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2516,7 +2522,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
       <c r="B41">
-        <v>7939.4458000000004</v>
+        <v>7292.7842000000001</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2524,7 +2530,7 @@
         <v>6.9800000000000001E-2</v>
       </c>
       <c r="B42">
-        <v>7961.0268999999998</v>
+        <v>7308.1196</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2532,7 +2538,7 @@
         <v>7.1599999999999997E-2</v>
       </c>
       <c r="B43">
-        <v>7981.5576000000001</v>
+        <v>7322.7109</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2540,7 +2546,7 @@
         <v>7.3300000000000004E-2</v>
       </c>
       <c r="B44">
-        <v>8001.1117999999997</v>
+        <v>7336.6089000000002</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2548,7 +2554,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="B45">
-        <v>8019.7578000000003</v>
+        <v>7349.8647000000001</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2556,7 +2562,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="B46">
-        <v>8037.5581000000002</v>
+        <v>7362.5234</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2564,7 +2570,7 @@
         <v>7.85E-2</v>
       </c>
       <c r="B47">
-        <v>8054.5684000000001</v>
+        <v>7374.6220999999996</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2572,7 +2578,7 @@
         <v>8.0299999999999996E-2</v>
       </c>
       <c r="B48">
-        <v>8070.8413</v>
+        <v>7386.1997000000001</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2580,7 +2586,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="B49">
-        <v>8086.4228999999996</v>
+        <v>7397.29</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2588,7 +2594,7 @@
         <v>8.3799999999999999E-2</v>
       </c>
       <c r="B50">
-        <v>8101.3563999999997</v>
+        <v>7407.9228999999996</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2596,7 +2602,7 @@
         <v>8.5500000000000007E-2</v>
       </c>
       <c r="B51">
-        <v>8115.6831000000002</v>
+        <v>7418.1255000000001</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2604,7 +2610,7 @@
         <v>8.7300000000000003E-2</v>
       </c>
       <c r="B52">
-        <v>8129.4359999999997</v>
+        <v>7427.9242999999997</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2612,7 +2618,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="B53">
-        <v>8142.6522999999997</v>
+        <v>7437.3446999999996</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2620,7 +2626,7 @@
         <v>9.0800000000000006E-2</v>
       </c>
       <c r="B54">
-        <v>8155.3608000000004</v>
+        <v>7446.4071999999996</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2628,7 +2634,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
       <c r="B55">
-        <v>8167.5913</v>
+        <v>7455.1318000000001</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2636,7 +2642,7 @@
         <v>9.4200000000000006E-2</v>
       </c>
       <c r="B56">
-        <v>8179.3711000000003</v>
+        <v>7463.5385999999999</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2644,7 +2650,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="B57">
-        <v>8190.7231000000002</v>
+        <v>7471.6436000000003</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2652,7 +2658,7 @@
         <v>9.7699999999999995E-2</v>
       </c>
       <c r="B58">
-        <v>8201.6708999999992</v>
+        <v>7479.4629000000004</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2660,7 +2666,7 @@
         <v>9.9500000000000005E-2</v>
       </c>
       <c r="B59">
-        <v>8212.2343999999994</v>
+        <v>7487.0117</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2668,7 +2674,7 @@
         <v>0.1012</v>
       </c>
       <c r="B60">
-        <v>8222.4375</v>
+        <v>7494.3062</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2676,7 +2682,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="B61">
-        <v>8232.2939000000006</v>
+        <v>7501.3563999999997</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2684,7 +2690,7 @@
         <v>0.1047</v>
       </c>
       <c r="B62">
-        <v>8241.8232000000007</v>
+        <v>7508.1747999999998</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2692,7 +2698,7 @@
         <v>0.1065</v>
       </c>
       <c r="B63">
-        <v>8251.0419999999995</v>
+        <v>7514.7754000000004</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2700,7 +2706,7 @@
         <v>0.1082</v>
       </c>
       <c r="B64">
-        <v>8259.9639000000006</v>
+        <v>7521.165</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2708,7 +2714,7 @@
         <v>0.11</v>
       </c>
       <c r="B65">
-        <v>8268.6034999999993</v>
+        <v>7527.3554999999997</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2716,7 +2722,7 @@
         <v>0.11169999999999999</v>
       </c>
       <c r="B66">
-        <v>8276.9745999999996</v>
+        <v>7533.3568999999998</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2724,7 +2730,7 @@
         <v>0.1134</v>
       </c>
       <c r="B67">
-        <v>8285.0879000000004</v>
+        <v>7539.1768000000002</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2732,7 +2738,7 @@
         <v>0.1152</v>
       </c>
       <c r="B68">
-        <v>8292.9580000000005</v>
+        <v>7544.8236999999999</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2740,7 +2746,7 @@
         <v>0.1169</v>
       </c>
       <c r="B69">
-        <v>8300.5946999999996</v>
+        <v>7550.3051999999998</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2748,7 +2754,7 @@
         <v>0.1187</v>
       </c>
       <c r="B70">
-        <v>8308.0059000000001</v>
+        <v>7555.6288999999997</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2756,7 +2762,7 @@
         <v>0.12039999999999999</v>
       </c>
       <c r="B71">
-        <v>8315.2041000000008</v>
+        <v>7560.8008</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2764,7 +2770,7 @@
         <v>0.1222</v>
       </c>
       <c r="B72">
-        <v>8322.1972999999998</v>
+        <v>7565.8280999999997</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2772,7 +2778,7 @@
         <v>0.1239</v>
       </c>
       <c r="B73">
-        <v>8328.9951000000001</v>
+        <v>7570.7168000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2780,7 +2786,7 @@
         <v>0.12570000000000001</v>
       </c>
       <c r="B74">
-        <v>8335.6054999999997</v>
+        <v>7575.4731000000002</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2788,7 +2794,7 @@
         <v>0.12740000000000001</v>
       </c>
       <c r="B75">
-        <v>8342.0342000000001</v>
+        <v>7580.1005999999998</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2796,7 +2802,7 @@
         <v>0.12920000000000001</v>
       </c>
       <c r="B76">
-        <v>8348.2909999999993</v>
+        <v>7584.6068999999998</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2804,7 +2810,7 @@
         <v>0.13089999999999999</v>
       </c>
       <c r="B77">
-        <v>8354.3817999999992</v>
+        <v>7588.9951000000001</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2812,7 +2818,7 @@
         <v>0.1326</v>
       </c>
       <c r="B78">
-        <v>8360.3125</v>
+        <v>7593.27</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2820,7 +2826,7 @@
         <v>0.13439999999999999</v>
       </c>
       <c r="B79">
-        <v>8366.0918000000001</v>
+        <v>7597.4375</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2828,7 +2834,7 @@
         <v>0.1361</v>
       </c>
       <c r="B80">
-        <v>8371.7217000000001</v>
+        <v>7601.4994999999999</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2836,7 +2842,7 @@
         <v>0.13789999999999999</v>
       </c>
       <c r="B81">
-        <v>8377.2109</v>
+        <v>7605.4614000000001</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2844,7 +2850,7 @@
         <v>0.1396</v>
       </c>
       <c r="B82">
-        <v>8382.5653999999995</v>
+        <v>7609.3266999999996</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2852,7 +2858,7 @@
         <v>0.1414</v>
       </c>
       <c r="B83">
-        <v>8387.7852000000003</v>
+        <v>7613.0977000000003</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2860,7 +2866,7 @@
         <v>0.1431</v>
       </c>
       <c r="B84">
-        <v>8392.8809000000001</v>
+        <v>7616.7803000000004</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2868,7 +2874,7 @@
         <v>0.1449</v>
       </c>
       <c r="B85">
-        <v>8397.8534999999993</v>
+        <v>7620.3760000000002</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2876,7 +2882,7 @@
         <v>0.14660000000000001</v>
       </c>
       <c r="B86">
-        <v>8402.7090000000007</v>
+        <v>7623.8872000000001</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2884,7 +2890,7 @@
         <v>0.1484</v>
       </c>
       <c r="B87">
-        <v>8407.4521000000004</v>
+        <v>7627.3188</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +2898,7 @@
         <v>0.15010000000000001</v>
       </c>
       <c r="B88">
-        <v>8412.0840000000007</v>
+        <v>7630.6724000000004</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2900,7 +2906,7 @@
         <v>0.15179999999999999</v>
       </c>
       <c r="B89">
-        <v>8416.6113000000005</v>
+        <v>7633.9507000000003</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2908,7 +2914,7 @@
         <v>0.15359999999999999</v>
       </c>
       <c r="B90">
-        <v>8421.0352000000003</v>
+        <v>7637.1562000000004</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2916,7 +2922,7 @@
         <v>0.15529999999999999</v>
       </c>
       <c r="B91">
-        <v>8425.3623000000007</v>
+        <v>7640.2910000000002</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2924,7 +2930,7 @@
         <v>0.15709999999999999</v>
       </c>
       <c r="B92">
-        <v>8429.5928000000004</v>
+        <v>7643.3584000000001</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2932,7 +2938,7 @@
         <v>0.1588</v>
       </c>
       <c r="B93">
-        <v>8433.7304999999997</v>
+        <v>7646.3599000000004</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2940,7 +2946,7 @@
         <v>0.16059999999999999</v>
       </c>
       <c r="B94">
-        <v>8437.7811999999994</v>
+        <v>7649.2983000000004</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2948,7 +2954,7 @@
         <v>0.1623</v>
       </c>
       <c r="B95">
-        <v>8441.7440999999999</v>
+        <v>7652.1747999999998</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2956,7 +2962,7 @@
         <v>0.1641</v>
       </c>
       <c r="B96">
-        <v>8445.6239999999998</v>
+        <v>7654.9921999999997</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2964,7 +2970,7 @@
         <v>0.1658</v>
       </c>
       <c r="B97">
-        <v>8449.4208999999992</v>
+        <v>7657.7510000000002</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2972,7 +2978,7 @@
         <v>0.1676</v>
       </c>
       <c r="B98">
-        <v>8453.1416000000008</v>
+        <v>7660.4540999999999</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2980,7 +2986,7 @@
         <v>0.16930000000000001</v>
       </c>
       <c r="B99">
-        <v>8456.7860999999994</v>
+        <v>7663.1045000000004</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2988,7 +2994,7 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="B100">
-        <v>8460.3554999999997</v>
+        <v>7665.7002000000002</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2996,7 +3002,7 @@
         <v>0.17280000000000001</v>
       </c>
       <c r="B101">
-        <v>8463.8554999999997</v>
+        <v>7668.2456000000002</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -3004,7 +3010,7 @@
         <v>0.17449999999999999</v>
       </c>
       <c r="B102">
-        <v>8467.2852000000003</v>
+        <v>7670.7416999999996</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -3012,7 +3018,7 @@
         <v>0.17630000000000001</v>
       </c>
       <c r="B103">
-        <v>8470.6465000000007</v>
+        <v>7673.1895000000004</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -3020,7 +3026,7 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="B104">
-        <v>8473.9434000000001</v>
+        <v>7675.5902999999998</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -3028,7 +3034,7 @@
         <v>0.17979999999999999</v>
       </c>
       <c r="B105">
-        <v>8477.1777000000002</v>
+        <v>7677.9462999999996</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -3036,7 +3042,7 @@
         <v>0.18149999999999999</v>
       </c>
       <c r="B106">
-        <v>8480.3505999999998</v>
+        <v>7680.2587999999996</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -3044,7 +3050,7 @@
         <v>0.18329999999999999</v>
       </c>
       <c r="B107">
-        <v>8483.4629000000004</v>
+        <v>7682.5282999999999</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -3052,7 +3058,7 @@
         <v>0.185</v>
       </c>
       <c r="B108">
-        <v>8486.5175999999992</v>
+        <v>7684.7559000000001</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -3060,7 +3066,7 @@
         <v>0.18679999999999999</v>
       </c>
       <c r="B109">
-        <v>8489.5146000000004</v>
+        <v>7686.9429</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -3068,7 +3074,7 @@
         <v>0.1885</v>
       </c>
       <c r="B110">
-        <v>8492.4590000000007</v>
+        <v>7689.0907999999999</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -3076,7 +3082,7 @@
         <v>0.19020000000000001</v>
       </c>
       <c r="B111">
-        <v>8495.3477000000003</v>
+        <v>7691.2007000000003</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -3084,7 +3090,7 @@
         <v>0.192</v>
       </c>
       <c r="B112">
-        <v>8498.1864999999998</v>
+        <v>7693.2734</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -3092,7 +3098,7 @@
         <v>0.19370000000000001</v>
       </c>
       <c r="B113">
-        <v>8500.9735999999994</v>
+        <v>7695.3091000000004</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -3100,7 +3106,7 @@
         <v>0.19550000000000001</v>
       </c>
       <c r="B114">
-        <v>8503.7119000000002</v>
+        <v>7697.3100999999997</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -3108,7 +3114,7 @@
         <v>0.19719999999999999</v>
       </c>
       <c r="B115">
-        <v>8506.4022999999997</v>
+        <v>7699.2768999999998</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -3116,7 +3122,7 @@
         <v>0.19900000000000001</v>
       </c>
       <c r="B116">
-        <v>8509.0458999999992</v>
+        <v>7701.2103999999999</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -3124,7 +3130,7 @@
         <v>0.20069999999999999</v>
       </c>
       <c r="B117">
-        <v>8511.6435999999994</v>
+        <v>7703.1103999999996</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -3132,7 +3138,7 @@
         <v>0.20250000000000001</v>
       </c>
       <c r="B118">
-        <v>8514.1991999999991</v>
+        <v>7704.9804999999997</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3140,7 +3146,7 @@
         <v>0.20419999999999999</v>
       </c>
       <c r="B119">
-        <v>8516.7090000000007</v>
+        <v>7706.8173999999999</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3148,7 +3154,7 @@
         <v>0.2059</v>
       </c>
       <c r="B120">
-        <v>8519.1787000000004</v>
+        <v>7708.6255000000001</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3156,7 +3162,7 @@
         <v>0.2077</v>
       </c>
       <c r="B121">
-        <v>8521.6074000000008</v>
+        <v>7710.4043000000001</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3164,7 +3170,7 @@
         <v>0.2094</v>
       </c>
       <c r="B122">
-        <v>8523.9961000000003</v>
+        <v>7712.1538</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3172,7 +3178,7 @@
         <v>0.2112</v>
       </c>
       <c r="B123">
-        <v>8526.3446999999996</v>
+        <v>7713.875</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3180,7 +3186,7 @@
         <v>0.21290000000000001</v>
       </c>
       <c r="B124">
-        <v>8528.6553000000004</v>
+        <v>7715.5698000000002</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3188,7 +3194,7 @@
         <v>0.2147</v>
       </c>
       <c r="B125">
-        <v>8530.9307000000008</v>
+        <v>7717.2372999999998</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3196,7 +3202,7 @@
         <v>0.21640000000000001</v>
       </c>
       <c r="B126">
-        <v>8533.1679999999997</v>
+        <v>7718.8788999999997</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3204,7 +3210,7 @@
         <v>0.21820000000000001</v>
       </c>
       <c r="B127">
-        <v>8535.3721000000005</v>
+        <v>7720.4951000000001</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3212,7 +3218,7 @@
         <v>0.21990000000000001</v>
       </c>
       <c r="B128">
-        <v>8537.5400000000009</v>
+        <v>7722.0864000000001</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3220,7 +3226,7 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="B129">
-        <v>8539.6748000000007</v>
+        <v>7723.6538</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3228,7 +3234,7 @@
         <v>0.22339999999999999</v>
       </c>
       <c r="B130">
-        <v>8541.7782999999999</v>
+        <v>7725.1986999999999</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3236,7 +3242,7 @@
         <v>0.22509999999999999</v>
       </c>
       <c r="B131">
-        <v>8543.8477000000003</v>
+        <v>7726.7191999999995</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3244,7 +3250,7 @@
         <v>0.22689999999999999</v>
       </c>
       <c r="B132">
-        <v>8545.8866999999991</v>
+        <v>7728.2168000000001</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3252,7 +3258,7 @@
         <v>0.2286</v>
       </c>
       <c r="B133">
-        <v>8547.8945000000003</v>
+        <v>7729.6934000000001</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3260,7 +3266,7 @@
         <v>0.23039999999999999</v>
       </c>
       <c r="B134">
-        <v>8549.8729999999996</v>
+        <v>7731.1475</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3268,7 +3274,7 @@
         <v>0.2321</v>
       </c>
       <c r="B135">
-        <v>8551.8212999999996</v>
+        <v>7732.5806000000002</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3276,7 +3282,7 @@
         <v>0.2339</v>
       </c>
       <c r="B136">
-        <v>8553.7432000000008</v>
+        <v>7733.9937</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3284,7 +3290,7 @@
         <v>0.2356</v>
       </c>
       <c r="B137">
-        <v>8555.6357000000007</v>
+        <v>7735.3856999999998</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3292,7 +3298,7 @@
         <v>0.2374</v>
       </c>
       <c r="B138">
-        <v>8557.5020000000004</v>
+        <v>7736.7587999999996</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3300,7 +3306,7 @@
         <v>0.23910000000000001</v>
       </c>
       <c r="B139">
-        <v>8559.3397999999997</v>
+        <v>7738.1127999999999</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3308,7 +3314,7 @@
         <v>0.2409</v>
       </c>
       <c r="B140">
-        <v>8561.1522999999997</v>
+        <v>7739.4462999999996</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3316,7 +3322,7 @@
         <v>0.24260000000000001</v>
       </c>
       <c r="B141">
-        <v>8562.9385000000002</v>
+        <v>7740.7622000000001</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3324,7 +3330,7 @@
         <v>0.24429999999999999</v>
       </c>
       <c r="B142">
-        <v>8564.7001999999993</v>
+        <v>7742.0600999999997</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3332,7 +3338,7 @@
         <v>0.24610000000000001</v>
       </c>
       <c r="B143">
-        <v>8566.4385000000002</v>
+        <v>7743.3402999999998</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3340,7 +3346,7 @@
         <v>0.24779999999999999</v>
       </c>
       <c r="B144">
-        <v>8568.1514000000006</v>
+        <v>7744.6035000000002</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3348,7 +3354,7 @@
         <v>0.24959999999999999</v>
       </c>
       <c r="B145">
-        <v>8569.8418000000001</v>
+        <v>7745.8495999999996</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3356,7 +3362,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="B146">
-        <v>8571.5077999999994</v>
+        <v>7747.0785999999998</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3364,7 +3370,7 @@
         <v>0.25309999999999999</v>
       </c>
       <c r="B147">
-        <v>8573.1522999999997</v>
+        <v>7748.2924999999996</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3372,7 +3378,7 @@
         <v>0.25480000000000003</v>
       </c>
       <c r="B148">
-        <v>8574.7754000000004</v>
+        <v>7749.4897000000001</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3380,7 +3386,7 @@
         <v>0.25659999999999999</v>
       </c>
       <c r="B149">
-        <v>8576.3760000000002</v>
+        <v>7750.6698999999999</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3388,7 +3394,7 @@
         <v>0.25829999999999997</v>
       </c>
       <c r="B150">
-        <v>8577.9550999999992</v>
+        <v>7751.8364000000001</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3396,7 +3402,7 @@
         <v>0.2601</v>
       </c>
       <c r="B151">
-        <v>8579.5146000000004</v>
+        <v>7752.9872999999998</v>
       </c>
     </row>
   </sheetData>
